--- a/final/armsoft-2026-10-15/update-loose-prices.xlsx
+++ b/final/armsoft-2026-10-15/update-loose-prices.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6500</v>
+        <v>7000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>sold loose — scale PLU 00107; zoovet's per-kg loose price; Siruk sells 100 g = 650</t>
+          <t>sold loose — scale PLU 00107; Siruk sells 100 g = 700</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5000</v>
+        <v>4100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>sold loose — scale PLU 00108; zoovet's per-kg loose price; Siruk sells 100 g = 500</t>
+          <t>sold loose — scale PLU 00108; Siruk sells 100 g = 410</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5000</v>
+        <v>4100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>sold loose — scale PLU 00109; zoovet's per-kg loose price; Siruk sells 100 g = 500</t>
+          <t>sold loose — scale PLU 00109; Siruk sells 100 g = 410</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5200</v>
+        <v>3700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>sold loose — scale PLU 00110; zoovet's per-kg loose price; Siruk sells 100 g = 520</t>
+          <t>sold loose — scale PLU 00110; Siruk sells 100 g = 370</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6000</v>
+        <v>5100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>sold loose — scale PLU 00111; zoovet's per-kg loose price; Siruk sells 100 g = 600</t>
+          <t>sold loose — scale PLU 00111; Siruk sells 100 g = 510</t>
         </is>
       </c>
     </row>

--- a/final/armsoft-2026-10-15/update-loose-prices.xlsx
+++ b/final/armsoft-2026-10-15/update-loose-prices.xlsx
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4100</v>
+        <v>5500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>sold loose — scale PLU 00108; Siruk sells 100 g = 410</t>
+          <t>sold loose — scale PLU 00108; Siruk sells 100 g = 550</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4100</v>
+        <v>5500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>sold loose — scale PLU 00109; Siruk sells 100 g = 410</t>
+          <t>sold loose — scale PLU 00109; Siruk sells 100 g = 550</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3700</v>
+        <v>5700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>sold loose — scale PLU 00110; Siruk sells 100 g = 370</t>
+          <t>sold loose — scale PLU 00110; Siruk sells 100 g = 570</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5100</v>
+        <v>6600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>sold loose — scale PLU 00111; Siruk sells 100 g = 510</t>
+          <t>sold loose — scale PLU 00111; Siruk sells 100 g = 660</t>
         </is>
       </c>
     </row>
